--- a/docs/StructureDefinition-retina-imagingstudy.xlsx
+++ b/docs/StructureDefinition-retina-imagingstudy.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$67</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2463" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2497" uniqueCount="515">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-30T22:57:21+01:00</t>
+    <t>2025-12-02</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -650,7 +650,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://sectra.no/identifiers</t>
+    <t>http://dips.no/fhir/RetinaIntegration/sectra-image-study-id</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -748,7 +748,7 @@
     <t>ImagingStudy.status</t>
   </si>
   <si>
-    <t>Status of the imaging study: registered | available.</t>
+    <t>Status of the imaging study: registered (SectraId identified) | available (Image information appended by AI system and is available).</t>
   </si>
   <si>
     <t>The current state of the ImagingStudy.</t>
@@ -1058,7 +1058,7 @@
 </t>
   </si>
   <si>
-    <t>Type of imaging procedure performed: fundus photography | OCT.</t>
+    <t>OCT or Fundus Photography procedure (after AI analysis).</t>
   </si>
   <si>
     <t>The code for the performed procedure type.</t>
@@ -1198,10 +1198,10 @@
 </t>
   </si>
   <si>
-    <t>We don't have any more information about the image series in this version of the API.</t>
-  </si>
-  <si>
-    <t>Each study has one or more series of images or other content.</t>
+    <t>Image series will be added by the AI system.</t>
+  </si>
+  <si>
+    <t>Collection of images organized by left eye, right eye.</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=COMP].target[classCode=OBSSER, moodCode=EVN]</t>
@@ -1240,7 +1240,7 @@
 </t>
   </si>
   <si>
-    <t>DICOM Series Instance UID for the series</t>
+    <t>Series Instance UID.</t>
   </si>
   <si>
     <t>The DICOM Series Instance UID for the series.</t>
@@ -1356,16 +1356,13 @@
 </t>
   </si>
   <si>
-    <t>Body part examined</t>
-  </si>
-  <si>
-    <t>The anatomic structures examined. See DICOM Part 16 Annex L (http://dicom.nema.org/medical/dicom/current/output/chtml/part16/chapter_L.html) for DICOM to SNOMED-CT mappings. The bodySite may indicate the laterality of body part imaged; if so, it shall be consistent with any content of ImagingStudy.series.laterality.</t>
-  </si>
-  <si>
-    <t>Codes describing anatomical locations. May include laterality.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
+    <t>Body site (eye) for this series.</t>
+  </si>
+  <si>
+    <t>Specifies which eye (left or right retina) this series documents. All images in a series must be from the same eye.</t>
+  </si>
+  <si>
+    <t>http://dips.no/fhir/RetinaIntegration/ValueSet/retina-body-site-vs</t>
   </si>
   <si>
     <t>.targetSiteCode</t>
@@ -1430,7 +1427,7 @@
 OperatorName</t>
   </si>
   <si>
-    <t>Who performed the series</t>
+    <t>Device that captured the images in this series.</t>
   </si>
   <si>
     <t>Indicates who or what performed the series and how they were involved.</t>
@@ -1482,6 +1479,9 @@
 </t>
   </si>
   <si>
+    <t>Who performed the series</t>
+  </si>
+  <si>
     <t>Indicates who or what performed the series.</t>
   </si>
   <si>
@@ -1497,10 +1497,10 @@
     <t>ImagingStudy.series.instance</t>
   </si>
   <si>
-    <t>A single SOP instance from the series</t>
-  </si>
-  <si>
-    <t>A single SOP instance within the series, e.g. an image, or presentation state.</t>
+    <t>Individual image instances in this series.</t>
+  </si>
+  <si>
+    <t>Each instance represents a single retinal image within this series.</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=COMP].target[classCode=DGIMG, moodCode=EVN]</t>
@@ -1510,6 +1510,26 @@
   </si>
   <si>
     <t>ImagingStudy.series.instance.extension</t>
+  </si>
+  <si>
+    <t>ImagingStudy.series.instance.extension:view</t>
+  </si>
+  <si>
+    <t>view</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://dips.no/fhir/RetinaIntegration/StructureDefinition/retinal-image-view}
+</t>
+  </si>
+  <si>
+    <t>Image view/centering</t>
+  </si>
+  <si>
+    <t>The centering or anatomical focus of this specific retinal image.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
   </si>
   <si>
     <t>ImagingStudy.series.instance.modifierExtension</t>
@@ -1522,10 +1542,10 @@
 </t>
   </si>
   <si>
-    <t>DICOM SOP Instance UID</t>
-  </si>
-  <si>
-    <t>The DICOM SOP Instance UID for this image or other DICOM content.</t>
+    <t>Image Instance UID.</t>
+  </si>
+  <si>
+    <t>Unique identifier for this individual image, generated by the AI system.</t>
   </si>
   <si>
     <t>See  [DICOM PS3.3 C.12.1](http://dicom.nema.org/medical/dicom/current/output/chtml/part03/sect_C.12.html#sect_C.12.1).</t>
@@ -1918,7 +1938,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO66"/>
+  <dimension ref="A1:AO67"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="40.8828125" customWidth="true" bestFit="true"/>
@@ -5719,7 +5739,7 @@
         <v>79</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>90</v>
@@ -6409,7 +6429,7 @@
         <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>21</v>
@@ -7570,7 +7590,7 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>89</v>
@@ -7618,13 +7638,11 @@
         <v>21</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="Y49" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="Y49" s="2"/>
+      <c r="Z49" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="Z49" t="s" s="2">
-        <v>432</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>21</v>
@@ -7660,10 +7678,10 @@
         <v>21</v>
       </c>
       <c r="AL49" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AM49" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>21</v>
@@ -7674,10 +7692,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7703,10 +7721,10 @@
         <v>247</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>437</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7736,11 +7754,11 @@
         <v>351</v>
       </c>
       <c r="Y50" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="Z50" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="Z50" t="s" s="2">
-        <v>439</v>
-      </c>
       <c r="AA50" t="s" s="2">
         <v>21</v>
       </c>
@@ -7757,7 +7775,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7775,10 +7793,10 @@
         <v>21</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>21</v>
@@ -7789,10 +7807,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7815,13 +7833,13 @@
         <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7872,7 +7890,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7890,10 +7908,10 @@
         <v>21</v>
       </c>
       <c r="AL51" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>21</v>
@@ -7904,10 +7922,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7933,10 +7951,10 @@
         <v>274</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7987,7 +8005,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -8008,7 +8026,7 @@
         <v>279</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>21</v>
@@ -8019,14 +8037,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8048,16 +8066,16 @@
         <v>378</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="N53" t="s" s="2">
+      <c r="O53" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>21</v>
@@ -8106,7 +8124,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8121,13 +8139,13 @@
         <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>302</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>21</v>
@@ -8138,10 +8156,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8253,10 +8271,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8370,10 +8388,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8489,10 +8507,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8518,14 +8536,14 @@
         <v>188</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>21</v>
@@ -8553,11 +8571,11 @@
         <v>193</v>
       </c>
       <c r="Y57" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="Z57" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="Z57" t="s" s="2">
-        <v>467</v>
-      </c>
       <c r="AA57" t="s" s="2">
         <v>21</v>
       </c>
@@ -8574,7 +8592,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8606,10 +8624,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8632,10 +8650,10 @@
         <v>90</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="M58" t="s" s="2">
         <v>470</v>
@@ -8689,7 +8707,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>89</v>
@@ -8732,7 +8750,7 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>80</v>
@@ -8958,11 +8976,11 @@
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>134</v>
+        <v>21</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>80</v>
@@ -8980,14 +8998,12 @@
         <v>135</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>21</v>
@@ -9024,16 +9040,14 @@
         <v>21</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="AC61" s="2"/>
       <c r="AD61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>21</v>
+        <v>153</v>
       </c>
       <c r="AF61" t="s" s="2">
         <v>174</v>
@@ -9054,7 +9068,7 @@
         <v>21</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>168</v>
+        <v>21</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>21</v>
@@ -9071,43 +9085,41 @@
         <v>480</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="C62" s="2"/>
+        <v>479</v>
+      </c>
+      <c r="C62" t="s" s="2">
+        <v>481</v>
+      </c>
       <c r="D62" t="s" s="2">
-        <v>385</v>
+        <v>21</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>135</v>
+        <v>482</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>386</v>
+        <v>483</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>388</v>
-      </c>
+        <v>484</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>21</v>
       </c>
@@ -9155,7 +9167,7 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>389</v>
+        <v>174</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9164,7 +9176,7 @@
         <v>80</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>21</v>
+        <v>485</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>140</v>
@@ -9173,7 +9185,7 @@
         <v>21</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>132</v>
+        <v>21</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>21</v>
@@ -9187,45 +9199,45 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>482</v>
+        <v>385</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>91</v>
+        <v>135</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>483</v>
+        <v>386</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>484</v>
+        <v>387</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>485</v>
+        <v>138</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>486</v>
+        <v>388</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>21</v>
@@ -9238,7 +9250,7 @@
         <v>21</v>
       </c>
       <c r="T63" t="s" s="2">
-        <v>487</v>
+        <v>21</v>
       </c>
       <c r="U63" t="s" s="2">
         <v>21</v>
@@ -9274,28 +9286,28 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>481</v>
+        <v>389</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>397</v>
+        <v>132</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>488</v>
+        <v>21</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>21</v>
@@ -9306,14 +9318,14 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -9332,16 +9344,20 @@
         <v>21</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>247</v>
+        <v>91</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="N64" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="O64" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="N64" s="2"/>
-      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>21</v>
       </c>
@@ -9353,7 +9369,7 @@
         <v>21</v>
       </c>
       <c r="T64" t="s" s="2">
-        <v>21</v>
+        <v>493</v>
       </c>
       <c r="U64" t="s" s="2">
         <v>21</v>
@@ -9365,13 +9381,13 @@
         <v>21</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>193</v>
+        <v>21</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>493</v>
+        <v>21</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>494</v>
+        <v>21</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>21</v>
@@ -9389,7 +9405,7 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>89</v>
@@ -9407,10 +9423,10 @@
         <v>21</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>495</v>
+        <v>397</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>21</v>
@@ -9421,18 +9437,18 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G65" t="s" s="2">
         <v>89</v>
@@ -9447,13 +9463,13 @@
         <v>21</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>314</v>
+        <v>247</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9468,7 +9484,7 @@
         <v>21</v>
       </c>
       <c r="T65" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="U65" t="s" s="2">
         <v>21</v>
@@ -9480,13 +9496,13 @@
         <v>21</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>21</v>
+        <v>193</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>21</v>
+        <v>499</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>21</v>
+        <v>500</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>21</v>
@@ -9504,10 +9520,10 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH65" t="s" s="2">
         <v>89</v>
@@ -9543,7 +9559,7 @@
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>21</v>
+        <v>504</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9562,17 +9578,15 @@
         <v>21</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>164</v>
+        <v>314</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="N66" t="s" s="2">
         <v>506</v>
       </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>21</v>
@@ -9585,7 +9599,7 @@
         <v>21</v>
       </c>
       <c r="T66" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="U66" t="s" s="2">
         <v>21</v>
@@ -9651,8 +9665,125 @@
         <v>21</v>
       </c>
     </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="O67" s="2"/>
+      <c r="P67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AO66">
+  <autoFilter ref="A1:AO67">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9662,7 +9793,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI65">
+  <conditionalFormatting sqref="A2:AI66">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-retina-imagingstudy.xlsx
+++ b/docs/StructureDefinition-retina-imagingstudy.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/docs/StructureDefinition-retina-imagingstudy.xlsx
+++ b/docs/StructureDefinition-retina-imagingstudy.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.8.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/docs/StructureDefinition-retina-imagingstudy.xlsx
+++ b/docs/StructureDefinition-retina-imagingstudy.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.0</t>
+    <t>0.8.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/docs/StructureDefinition-retina-imagingstudy.xlsx
+++ b/docs/StructureDefinition-retina-imagingstudy.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.1</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/docs/StructureDefinition-retina-imagingstudy.xlsx
+++ b/docs/StructureDefinition-retina-imagingstudy.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.9.1</t>
   </si>
   <si>
     <t>Name</t>
